--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484182_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484182_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.7508</v>
+        <v>5.4533</v>
       </c>
       <c r="E2" t="n">
-        <v>4.8521</v>
+        <v>3.6107</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8987</v>
+        <v>1.8426</v>
       </c>
       <c r="G2" t="n">
         <v>2.0282</v>
@@ -610,13 +610,13 @@
         <v>0.5952</v>
       </c>
       <c r="S2" t="n">
-        <v>1.9805</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>1.6609</v>
+        <v>0.4195</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3196</v>
+        <v>0.2635</v>
       </c>
       <c r="V2" t="n">
         <v>2.1469</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.8331</v>
+        <v>4.268</v>
       </c>
       <c r="E3" t="n">
-        <v>4.3877</v>
+        <v>4.5521</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4454</v>
+        <v>-0.2841</v>
       </c>
       <c r="G3" t="n">
         <v>2.1113</v>
@@ -688,13 +688,13 @@
         <v>1.3887</v>
       </c>
       <c r="S3" t="n">
-        <v>2.325</v>
+        <v>1.7599</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4876</v>
+        <v>0.6519</v>
       </c>
       <c r="U3" t="n">
-        <v>1.8374</v>
+        <v>1.108</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. SARRATE CARRILLO</t>
+          <t>C. DICKERSON</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.277</v>
+        <v>3.6926</v>
       </c>
       <c r="E4" t="n">
-        <v>2.9733</v>
+        <v>3.4425</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3038</v>
+        <v>0.2501</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.7695</v>
+        <v>1.9147</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.826</v>
+        <v>-0.1868</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.9435</v>
+        <v>2.1014</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.4167</v>
+        <v>2.6837</v>
       </c>
       <c r="K4" t="n">
-        <v>1.3625</v>
+        <v>1.2755</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.7792</v>
+        <v>1.4082</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.3527</v>
+        <v>-0.769</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.1885</v>
+        <v>-1.4622</v>
       </c>
       <c r="O4" t="n">
-        <v>0.8357</v>
+        <v>0.6932</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5952</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q4" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5871</v>
+        <v>0.5952</v>
       </c>
       <c r="S4" t="n">
-        <v>1.4352</v>
+        <v>0.897</v>
       </c>
       <c r="T4" t="n">
-        <v>1.0998</v>
+        <v>0.5442</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3354</v>
+        <v>0.3527</v>
       </c>
       <c r="V4" t="n">
-        <v>3.0162</v>
+        <v>1.2777</v>
       </c>
       <c r="W4" t="n">
-        <v>3.2821</v>
+        <v>1.2065</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.266</v>
+        <v>0.0713</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C. DICKERSON</t>
+          <t>P. SARRATE CARRILLO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.7531</v>
+        <v>3.3326</v>
       </c>
       <c r="E5" t="n">
-        <v>2.6432</v>
+        <v>2.9166</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1099</v>
+        <v>0.416</v>
       </c>
       <c r="G5" t="n">
-        <v>1.9147</v>
+        <v>-1.7695</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1868</v>
+        <v>-0.826</v>
       </c>
       <c r="I5" t="n">
-        <v>2.1014</v>
+        <v>-0.9435</v>
       </c>
       <c r="J5" t="n">
-        <v>2.6837</v>
+        <v>-0.4167</v>
       </c>
       <c r="K5" t="n">
-        <v>1.2755</v>
+        <v>1.3625</v>
       </c>
       <c r="L5" t="n">
-        <v>1.4082</v>
+        <v>-1.7792</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.769</v>
+        <v>-1.3527</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.4622</v>
+        <v>-2.1885</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6932</v>
+        <v>0.8357</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.3968</v>
+        <v>0.5952</v>
       </c>
       <c r="Q5" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5952</v>
+        <v>1.5871</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0425</v>
+        <v>1.4907</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.255</v>
+        <v>1.0431</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2125</v>
+        <v>0.4476</v>
       </c>
       <c r="V5" t="n">
-        <v>1.2777</v>
+        <v>3.0162</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2065</v>
+        <v>3.2821</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0713</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6344</v>
+        <v>2.3074</v>
       </c>
       <c r="E6" t="n">
-        <v>2.5261</v>
+        <v>3.0589</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8918</v>
+        <v>-0.7514999999999999</v>
       </c>
       <c r="G6" t="n">
         <v>1.9416</v>
@@ -922,13 +922,13 @@
         <v>1.3887</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0425</v>
+        <v>0.7156</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1303</v>
+        <v>0.4025</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1728</v>
+        <v>0.3131</v>
       </c>
       <c r="V6" t="n">
         <v>-1.7384</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. NGUBA ETAME</t>
+          <t>E. IBAEZ ALDAZABAL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4368</v>
+        <v>0.2333</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8642</v>
+        <v>-0.9633</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4275</v>
+        <v>1.1966</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.0568</v>
+        <v>0.0165</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.3199</v>
+        <v>1.4663</v>
       </c>
       <c r="I7" t="n">
-        <v>0.263</v>
+        <v>-1.4498</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2775</v>
+        <v>-0.2718</v>
       </c>
       <c r="K7" t="n">
-        <v>0.157</v>
+        <v>1.0484</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1205</v>
+        <v>-1.3202</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.3343</v>
+        <v>0.2883</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.4769</v>
+        <v>0.4179</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1425</v>
+        <v>-0.1295</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5952</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R7" t="n">
         <v>0.5952</v>
       </c>
       <c r="S7" t="n">
-        <v>1.2357</v>
+        <v>0.6135</v>
       </c>
       <c r="T7" t="n">
-        <v>0.924</v>
+        <v>0.3004</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3117</v>
+        <v>0.3131</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3373</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.3373</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E. IBAEZ ALDAZABAL</t>
+          <t>D. NGUBA ETAME</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3571</v>
+        <v>0.2327</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.6378</v>
+        <v>0.6602</v>
       </c>
       <c r="F8" t="n">
-        <v>1.2808</v>
+        <v>-0.4275</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0165</v>
+        <v>-1.0568</v>
       </c>
       <c r="H8" t="n">
-        <v>1.4663</v>
+        <v>-1.3199</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.4498</v>
+        <v>0.263</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2718</v>
+        <v>0.2775</v>
       </c>
       <c r="K8" t="n">
-        <v>1.0484</v>
+        <v>0.157</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.3202</v>
+        <v>0.1205</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2883</v>
+        <v>-1.3343</v>
       </c>
       <c r="N8" t="n">
-        <v>0.4179</v>
+        <v>-1.4769</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1295</v>
+        <v>0.1425</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.3968</v>
+        <v>0.5952</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0.5952</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0232</v>
+        <v>1.0316</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3741</v>
+        <v>0.7199</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3973</v>
+        <v>0.3117</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.3373</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.3373</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. NDOUR</t>
+          <t>V. VINÓS ALTEMIR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.7894</v>
+        <v>-1.4224</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.2455</v>
+        <v>-1.1455</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5439000000000001</v>
+        <v>-0.2769</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4795</v>
+        <v>-1.3657</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.872</v>
+        <v>-0.5495</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3926</v>
+        <v>-0.8162</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1205</v>
+        <v>-1.0378</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>0.3226</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1205</v>
+        <v>-1.3604</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6</v>
+        <v>-0.3279</v>
       </c>
       <c r="N9" t="n">
         <v>-0.872</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2721</v>
+        <v>0.5442</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.9838</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9838</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.674</v>
+        <v>-0.0567</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6178</v>
+        <v>-0.1077</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0561</v>
+        <v>0.051</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>V. VINÓS ALTEMIR</t>
+          <t>S. NDOUR</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.801</v>
+        <v>-2.0113</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4119</v>
+        <v>-1.5516</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3891</v>
+        <v>-0.4597</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.3657</v>
+        <v>-0.4795</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5495</v>
+        <v>-0.872</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8162</v>
+        <v>0.3926</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.0378</v>
+        <v>0.1205</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3226</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.3604</v>
+        <v>0.1205</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.3279</v>
+        <v>-0.6</v>
       </c>
       <c r="N10" t="n">
         <v>-0.872</v>
       </c>
       <c r="O10" t="n">
-        <v>0.5442</v>
+        <v>0.2721</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-1.9838</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.9838</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4353</v>
+        <v>0.452</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3741</v>
+        <v>0.3118</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0612</v>
+        <v>0.1403</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.0489</v>
+        <v>-2.6869</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.9373</v>
+        <v>-3.3228</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8884</v>
+        <v>0.6359</v>
       </c>
       <c r="G11" t="n">
         <v>-2.3284</v>
@@ -1312,13 +1312,13 @@
         <v>0.1984</v>
       </c>
       <c r="S11" t="n">
-        <v>1.073</v>
+        <v>0.435</v>
       </c>
       <c r="T11" t="n">
-        <v>0.6746</v>
+        <v>0.2891</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3984</v>
+        <v>0.1459</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.7694</v>
+        <v>-3.2331</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.3684</v>
+        <v>-4.3651</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5989</v>
+        <v>1.132</v>
       </c>
       <c r="G12" t="n">
         <v>-2.7981</v>
@@ -1390,13 +1390,13 @@
         <v>0.9919</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9993</v>
+        <v>0.537</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8161</v>
+        <v>0.1872</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1832</v>
+        <v>0.3499</v>
       </c>
       <c r="V12" t="n">
         <v>1.0118</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.919400000000003</v>
+        <v>10.1662</v>
       </c>
       <c r="E13" t="n">
-        <v>5.645699999999999</v>
+        <v>6.8927</v>
       </c>
       <c r="F13" t="n">
-        <v>3.2736</v>
+        <v>3.2735</v>
       </c>
       <c r="G13" t="n">
         <v>-1.785699999999999</v>
@@ -1468,10 +1468,10 @@
         <v>7.935600000000001</v>
       </c>
       <c r="S13" t="n">
-        <v>7.312000000000001</v>
+        <v>8.5586</v>
       </c>
       <c r="T13" t="n">
-        <v>3.515100000000001</v>
+        <v>4.761900000000001</v>
       </c>
       <c r="U13" t="n">
         <v>3.7968</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.3087</v>
+        <v>3.1047</v>
       </c>
       <c r="E14" t="n">
-        <v>2.647</v>
+        <v>2.443</v>
       </c>
       <c r="F14" t="n">
         <v>0.6617</v>
@@ -1546,10 +1546,10 @@
         <v>1.3887</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.6575</v>
+        <v>-0.8616</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0735</v>
+        <v>-0.2776</v>
       </c>
       <c r="U14" t="n">
         <v>-0.5839</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9187</v>
+        <v>1.1049</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3496</v>
+        <v>0.4516</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5691000000000001</v>
+        <v>0.6533</v>
       </c>
       <c r="G15" t="n">
         <v>0.7828000000000001</v>
@@ -1624,13 +1624,13 @@
         <v>0.1984</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2035</v>
+        <v>0.3897</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0567</v>
+        <v>0.1588</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1468</v>
+        <v>0.2309</v>
       </c>
       <c r="V15" t="n">
         <v>-0.266</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4409</v>
+        <v>0.4613</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8838</v>
+        <v>1.6798</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.4429</v>
+        <v>-1.2184</v>
       </c>
       <c r="G16" t="n">
         <v>0.5973000000000001</v>
@@ -1702,13 +1702,13 @@
         <v>1.5871</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8706</v>
+        <v>-0.8502</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2606</v>
+        <v>-0.4646</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.61</v>
+        <v>-0.3856</v>
       </c>
       <c r="V16" t="n">
         <v>-0.6745</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1975</v>
+        <v>-0.6749000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2279</v>
+        <v>0.4117</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.0304</v>
+        <v>-1.0865</v>
       </c>
       <c r="G17" t="n">
         <v>0.2369</v>
@@ -1780,13 +1780,13 @@
         <v>1.5871</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5589</v>
+        <v>-1.4312</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4252</v>
+        <v>-0.391</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.9841</v>
+        <v>-1.0402</v>
       </c>
       <c r="V17" t="n">
         <v>-0.8692</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>B. BORRERO PERLAZA</t>
+          <t>P. SANTIAGO PAZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.1718</v>
+        <v>-0.8891</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.7358</v>
+        <v>-1.5469</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.436</v>
+        <v>0.6578000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3104</v>
+        <v>1.6395</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6653</v>
+        <v>0.2118</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.355</v>
+        <v>1.4277</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6301</v>
+        <v>0.5105</v>
       </c>
       <c r="K18" t="n">
-        <v>0.59</v>
+        <v>1.2659</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0402</v>
+        <v>-0.7554</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.3198</v>
+        <v>1.129</v>
       </c>
       <c r="N18" t="n">
-        <v>0.07530000000000001</v>
+        <v>-1.0541</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3951</v>
+        <v>2.1831</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.7935</v>
+        <v>0.1984</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9919</v>
+        <v>-1.1903</v>
       </c>
       <c r="R18" t="n">
-        <v>0.1984</v>
+        <v>1.3887</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6887</v>
+        <v>-1.5205</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3741</v>
+        <v>-0.8671</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3146</v>
+        <v>-0.6534</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-1.2065</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. SANTIAGO PAZ</t>
+          <t>B. BORRERO PERLAZA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.4528</v>
+        <v>-1.0316</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.3631</v>
+        <v>-0.7358</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9103</v>
+        <v>-0.2957</v>
       </c>
       <c r="G19" t="n">
-        <v>1.6395</v>
+        <v>0.3104</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2118</v>
+        <v>0.6653</v>
       </c>
       <c r="I19" t="n">
-        <v>1.4277</v>
+        <v>-0.355</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5105</v>
+        <v>0.6301</v>
       </c>
       <c r="K19" t="n">
-        <v>1.2659</v>
+        <v>0.59</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.7554</v>
+        <v>0.0402</v>
       </c>
       <c r="M19" t="n">
-        <v>1.129</v>
+        <v>-0.3198</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.0541</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="O19" t="n">
-        <v>2.1831</v>
+        <v>-0.3951</v>
       </c>
       <c r="P19" t="n">
+        <v>-0.7935</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>-0.9919</v>
+      </c>
+      <c r="R19" t="n">
         <v>0.1984</v>
       </c>
-      <c r="Q19" t="n">
-        <v>-1.1903</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.3887</v>
-      </c>
       <c r="S19" t="n">
-        <v>-2.0842</v>
+        <v>-0.5484</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.6833</v>
+        <v>-0.3741</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4009</v>
+        <v>-0.1743</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.2065</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2065</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6817</v>
+        <v>-1.5899</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.6304</v>
+        <v>-1.4264</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0513</v>
+        <v>-0.1635</v>
       </c>
       <c r="G20" t="n">
         <v>-0.3316</v>
@@ -2014,13 +2014,13 @@
         <v>0.3968</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5566</v>
+        <v>-0.4648</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5611</v>
+        <v>-0.357</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0045</v>
+        <v>-0.1077</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.2138</v>
+        <v>-1.7215</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.8312</v>
+        <v>-0.423</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.3826</v>
+        <v>-1.2985</v>
       </c>
       <c r="G21" t="n">
         <v>-2.2852</v>
@@ -2092,13 +2092,13 @@
         <v>0.7935</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2702</v>
+        <v>-0.778</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9975000000000001</v>
+        <v>-0.5894</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2727</v>
+        <v>-0.1885</v>
       </c>
       <c r="V21" t="n">
         <v>1.7384</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.469</v>
+        <v>-3.1246</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.1359</v>
+        <v>-0.9318</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.3331</v>
+        <v>-2.1928</v>
       </c>
       <c r="G22" t="n">
         <v>-0.9568</v>
@@ -2170,13 +2170,13 @@
         <v>0.7935</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.1705</v>
+        <v>-0.8260999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6235000000000001</v>
+        <v>-0.4194</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.547</v>
+        <v>-0.4068</v>
       </c>
       <c r="V22" t="n">
         <v>-1.7384</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.7962</v>
+        <v>-4.5588</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.6855</v>
+        <v>-3.1956</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.1107</v>
+        <v>-1.3632</v>
       </c>
       <c r="G23" t="n">
         <v>-0.523</v>
@@ -2248,13 +2248,13 @@
         <v>1.5871</v>
       </c>
       <c r="S23" t="n">
-        <v>0.3418</v>
+        <v>-0.4209</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2949</v>
+        <v>-0.2152</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0469</v>
+        <v>-0.2056</v>
       </c>
       <c r="V23" t="n">
         <v>-2.8215</v>
@@ -2284,10 +2284,10 @@
         <v>-8.919499999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.273600000000001</v>
+        <v>-3.2734</v>
       </c>
       <c r="F24" t="n">
-        <v>-5.645899999999999</v>
+        <v>-5.6458</v>
       </c>
       <c r="G24" t="n">
         <v>1.7855</v>
@@ -2326,13 +2326,13 @@
         <v>9.9193</v>
       </c>
       <c r="S24" t="n">
-        <v>-7.311900000000001</v>
+        <v>-7.312</v>
       </c>
       <c r="T24" t="n">
-        <v>-3.7968</v>
+        <v>-3.7966</v>
       </c>
       <c r="U24" t="n">
-        <v>-3.515</v>
+        <v>-3.5151</v>
       </c>
       <c r="V24" t="n">
         <v>-5.376999999999999</v>
